--- a/CPRD Raw Analysis/Results/Overall/overall_combined_bootstrap_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Overall/overall_combined_bootstrap_summary_costs_SOURCE.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,145 +418,71 @@
         </is>
       </c>
       <c r="B2">
-        <v>757.307</v>
+        <v>1112.792</v>
       </c>
       <c r="C2">
-        <v>26.374</v>
+        <v>57.186</v>
       </c>
       <c r="D2">
-        <v>5.136</v>
+        <v>7.562</v>
       </c>
       <c r="E2">
-        <v>0.162</v>
+        <v>0.239</v>
       </c>
       <c r="F2">
-        <v>748.009</v>
+        <v>1099.222</v>
       </c>
       <c r="G2">
-        <v>768.14</v>
+        <v>1128.865</v>
       </c>
       <c r="H2">
-        <v>747.563</v>
+        <v>1098.476</v>
       </c>
       <c r="I2">
-        <v>768.098</v>
+        <v>1128.562</v>
       </c>
       <c r="J2">
-        <v>747.283</v>
+        <v>1098.274</v>
       </c>
       <c r="K2">
-        <v>767.818</v>
+        <v>1128.359</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B3">
-        <v>728.736</v>
+        <v>1144.095</v>
       </c>
       <c r="C3">
-        <v>22.465</v>
+        <v>63.552</v>
       </c>
       <c r="D3">
-        <v>4.74</v>
+        <v>7.972</v>
       </c>
       <c r="E3">
-        <v>0.15</v>
+        <v>0.252</v>
       </c>
       <c r="F3">
-        <v>719.586</v>
+        <v>1128.792</v>
       </c>
       <c r="G3">
-        <v>738.165</v>
+        <v>1160.041</v>
       </c>
       <c r="H3">
-        <v>719.466</v>
+        <v>1128.561</v>
       </c>
       <c r="I3">
-        <v>738.154</v>
+        <v>1160.824</v>
       </c>
       <c r="J3">
-        <v>719.457</v>
+        <v>1127.688</v>
       </c>
       <c r="K3">
-        <v>738.145</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>779.0650000000001</v>
-      </c>
-      <c r="C4">
-        <v>25.167</v>
-      </c>
-      <c r="D4">
-        <v>5.017</v>
-      </c>
-      <c r="E4">
-        <v>0.159</v>
-      </c>
-      <c r="F4">
-        <v>769.259</v>
-      </c>
-      <c r="G4">
-        <v>788.924</v>
-      </c>
-      <c r="H4">
-        <v>769.409</v>
-      </c>
-      <c r="I4">
-        <v>789.498</v>
-      </c>
-      <c r="J4">
-        <v>768.659</v>
-      </c>
-      <c r="K4">
-        <v>788.748</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>749.563</v>
-      </c>
-      <c r="C5">
-        <v>23.914</v>
-      </c>
-      <c r="D5">
-        <v>4.89</v>
-      </c>
-      <c r="E5">
-        <v>0.155</v>
-      </c>
-      <c r="F5">
-        <v>739.987</v>
-      </c>
-      <c r="G5">
-        <v>759.1559999999999</v>
-      </c>
-      <c r="H5">
-        <v>739.768</v>
-      </c>
-      <c r="I5">
-        <v>759.405</v>
-      </c>
-      <c r="J5">
-        <v>739.73</v>
-      </c>
-      <c r="K5">
-        <v>759.367</v>
+        <v>1159.951</v>
       </c>
     </row>
   </sheetData>
